--- a/sample/datos_ejemplo.xlsx
+++ b/sample/datos_ejemplo.xlsx
@@ -31,20 +31,15 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE600"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,13 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +611,6 @@
           <t>Grafica4 · URL</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -853,7 +855,6 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1161,8 +1162,10 @@
           <t>miguel.hernandezmartinez@mercadolibre.com.mx</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1191,8 +1194,10 @@
           <t>steven.seedorf@mercadolibre.com.mx</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1221,8 +1226,10 @@
           <t>mariana.novoa@mercadolibre.com.mx</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1251,8 +1258,10 @@
           <t>ana.vargasfuentes@mercadolibre.com.mx</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>3</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1281,8 +1290,10 @@
           <t>garcia.gjuan@mercadolibre.com.mx</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>3</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1311,8 +1322,10 @@
           <t>eduardo.garcia@mercadolibre.com.mx</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>3</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1341,8 +1354,10 @@
           <t>carlosricardo.almanzaloo@mercadolibre.com.mx</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>3</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
